--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486687_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486687_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3098</v>
+        <v>2.5431</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4058</v>
+        <v>4.6887</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.096</v>
+        <v>-2.1457</v>
       </c>
       <c r="G2" t="n">
         <v>2.3614</v>
@@ -610,13 +610,13 @@
         <v>0.5792</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9251</v>
+        <v>1.1584</v>
       </c>
       <c r="T2" t="n">
-        <v>1.489</v>
+        <v>0.772</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4361</v>
+        <v>0.3865</v>
       </c>
       <c r="V2" t="n">
         <v>-1.5559</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3276</v>
+        <v>0.6959</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5195</v>
+        <v>0.7885</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1919</v>
+        <v>-0.0926</v>
       </c>
       <c r="G3" t="n">
         <v>-0.1505</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2097</v>
+        <v>0.1586</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1108</v>
+        <v>0.1581</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0989</v>
+        <v>0.0005</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8568</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. HERNÁNDEZ TRUJILLO</t>
+          <t>M. VILLANUEVA CUBELO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6499</v>
+        <v>0.0766</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2627</v>
+        <v>-0.6066</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9126</v>
+        <v>0.6833</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.9888</v>
+        <v>-1.0211</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3521</v>
+        <v>-1.4485</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6367</v>
+        <v>0.4273</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5293</v>
+        <v>0.2625</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0967</v>
+        <v>-0.2756</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5674</v>
+        <v>0.5381</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5181</v>
+        <v>-1.2837</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4488</v>
+        <v>-1.1728</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0693</v>
+        <v>-0.1108</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2118</v>
+        <v>-0.1379</v>
       </c>
       <c r="T4" t="n">
-        <v>2.344</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1322</v>
+        <v>-0.2342</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2856</v>
+        <v>0.6565</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. VILLANUEVA CUBELO</t>
+          <t>D. RUEDA ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7232</v>
+        <v>-0.8603</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2823</v>
+        <v>1.4685</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5591</v>
+        <v>-2.3288</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0211</v>
+        <v>2.0691</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4485</v>
+        <v>2.1934</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4273</v>
+        <v>-0.1243</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2625</v>
+        <v>6.2641</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2756</v>
+        <v>3.1601</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5381</v>
+        <v>3.104</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2837</v>
+        <v>-4.195</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1728</v>
+        <v>-0.9667</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1108</v>
+        <v>-3.2283</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5792</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>-4.827</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5446</v>
+        <v>3.2823</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9378</v>
+        <v>0.2138</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5795</v>
+        <v>0.1166</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3583</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6565</v>
+        <v>-1.5985</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.0852</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6565</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7817</v>
+        <v>-0.8892</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3164</v>
+        <v>-0.5232</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4653</v>
+        <v>-0.3659</v>
       </c>
       <c r="G6" t="n">
         <v>-1.7855</v>
@@ -922,13 +922,13 @@
         <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2315</v>
+        <v>0.124</v>
       </c>
       <c r="T6" t="n">
-        <v>0.248</v>
+        <v>0.0412</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0165</v>
+        <v>0.0828</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. RUEDA ALVAREZ</t>
+          <t>H. CARRON GRILLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7358</v>
+        <v>-1.8903</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2205</v>
+        <v>-1.8142</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9563</v>
+        <v>-0.076</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0691</v>
+        <v>-0.8973</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1934</v>
+        <v>0.0205</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1243</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>6.2641</v>
+        <v>-0.6281</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1601</v>
+        <v>0.0207</v>
       </c>
       <c r="L7" t="n">
-        <v>3.104</v>
+        <v>-0.6488</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.195</v>
+        <v>-0.2692</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9667</v>
+        <v>-0.0002</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.2283</v>
+        <v>-0.269</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5446</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.827</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>3.2823</v>
+        <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.4137</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1314</v>
+        <v>-0.2207</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4696</v>
+        <v>-0.193</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5985</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0852</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. CARRON GRILLO</t>
+          <t>J. HERNÁNDEZ TRUJILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9399</v>
+        <v>-2.0481</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8142</v>
+        <v>-1.1852</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1257</v>
+        <v>-0.8629</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8973</v>
+        <v>-1.9888</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0205</v>
+        <v>-0.3521</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-1.6367</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6281</v>
+        <v>0.5293</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0207</v>
+        <v>1.0967</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6488</v>
+        <v>-0.5674</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2692</v>
+        <v>-2.5181</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0002</v>
+        <v>-1.4488</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.269</v>
+        <v>-1.0693</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5792</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3862</v>
+        <v>1.7377</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4634</v>
+        <v>0.8136</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2207</v>
+        <v>0.8961</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2427</v>
+        <v>-0.0825</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2358</v>
+        <v>-3.5808</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9522</v>
+        <v>-1.173</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2836</v>
+        <v>-2.4077</v>
       </c>
       <c r="G9" t="n">
         <v>-3.3835</v>
@@ -1156,13 +1156,13 @@
         <v>1.3515</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9101</v>
+        <v>-0.2552</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.745</v>
+        <v>0.0341</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1651</v>
+        <v>-0.2893</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3282</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.1999</v>
+        <v>-6.7363</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3317</v>
+        <v>-4.1662</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8681</v>
+        <v>-2.5701</v>
       </c>
       <c r="G10" t="n">
         <v>-5.74</v>
@@ -1234,13 +1234,13 @@
         <v>3.0892</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4912</v>
+        <v>-0.0277</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3027</v>
+        <v>0.4683</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.4959</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1271</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.0373</v>
+        <v>-8.148999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3449</v>
+        <v>-5.2827</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6925</v>
+        <v>-2.8663</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5315</v>
@@ -1312,13 +1312,13 @@
         <v>2.1239</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.5723</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3304</v>
+        <v>0.3925</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3536</v>
+        <v>0.1798</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5559</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-21.6661</v>
+        <v>-20.8384</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.6332</v>
+        <v>-7.805400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.0329</v>
+        <v>-13.0327</v>
       </c>
       <c r="G12" t="n">
         <v>-13.0677</v>
@@ -1369,7 +1369,7 @@
         <v>2.4198</v>
       </c>
       <c r="L12" t="n">
-        <v>7.1783</v>
+        <v>7.178299999999998</v>
       </c>
       <c r="M12" t="n">
         <v>-22.6661</v>
@@ -1390,13 +1390,13 @@
         <v>17.3769</v>
       </c>
       <c r="S12" t="n">
-        <v>1.378400000000001</v>
+        <v>2.2062</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9267</v>
+        <v>2.7544</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5483000000000001</v>
+        <v>-0.5481</v>
       </c>
       <c r="V12" t="n">
         <v>-7.0803</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.4837</v>
+        <v>12.1869</v>
       </c>
       <c r="E13" t="n">
-        <v>8.774900000000001</v>
+        <v>9.188599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7088</v>
+        <v>2.9983</v>
       </c>
       <c r="G13" t="n">
         <v>13.4231</v>
@@ -1468,13 +1468,13 @@
         <v>3.6685</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6065</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2211</v>
+        <v>0.1926</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3854</v>
+        <v>-0.0959</v>
       </c>
       <c r="V13" t="n">
         <v>1.7563</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.8087</v>
+        <v>7.9743</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6755</v>
+        <v>5.9516</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1331</v>
+        <v>2.0227</v>
       </c>
       <c r="G14" t="n">
         <v>3.3378</v>
@@ -1546,13 +1546,13 @@
         <v>3.8616</v>
       </c>
       <c r="S14" t="n">
-        <v>1.324</v>
+        <v>0.4896</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9648</v>
+        <v>0.2408</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3592</v>
+        <v>0.2488</v>
       </c>
       <c r="V14" t="n">
         <v>1.2507</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8937</v>
+        <v>4.5364</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8288</v>
+        <v>2.0357</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0649</v>
+        <v>2.5007</v>
       </c>
       <c r="G15" t="n">
         <v>1.5655</v>
@@ -1624,13 +1624,13 @@
         <v>2.51</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4634</v>
+        <v>0.1793</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0279</v>
+        <v>0.179</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4355</v>
+        <v>0.0004</v>
       </c>
       <c r="V15" t="n">
         <v>2.2124</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3756</v>
+        <v>2.7656</v>
       </c>
       <c r="E16" t="n">
-        <v>0.844</v>
+        <v>1.6253</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5316</v>
+        <v>1.1403</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3917</v>
+        <v>-0.3929</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1305</v>
+        <v>-2.8479</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5221</v>
+        <v>2.4551</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0555</v>
+        <v>1.4088</v>
       </c>
       <c r="K16" t="n">
-        <v>0.629</v>
+        <v>-1.8127</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4265</v>
+        <v>3.2215</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6638</v>
+        <v>-1.8017</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7594</v>
+        <v>-1.0352</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9044</v>
+        <v>-0.7665</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3515</v>
+        <v>2.3169</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
         <v>3.2823</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1806</v>
+        <v>-0.3861</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0475</v>
+        <v>-0.3314</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1331</v>
+        <v>-0.0546</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5482</v>
+        <v>1.2277</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3282</v>
+        <v>1.5133</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.22</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8378</v>
+        <v>2.1825</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1513</v>
+        <v>1.3581</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6865</v>
+        <v>0.8244</v>
       </c>
       <c r="G17" t="n">
         <v>1.7096</v>
@@ -1780,13 +1780,13 @@
         <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3585</v>
+        <v>-0.0138</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2759</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.08260000000000001</v>
+        <v>0.0553</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2856</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>R. SANCHEZ CASTILLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3756</v>
+        <v>1.4539</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.2718</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5777</v>
+        <v>1.1821</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3929</v>
+        <v>0.4711</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.8479</v>
+        <v>0.6339</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4551</v>
+        <v>-0.1628</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4088</v>
+        <v>0.8582</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.8127</v>
+        <v>0.0828</v>
       </c>
       <c r="L18" t="n">
-        <v>3.2215</v>
+        <v>0.7754</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8017</v>
+        <v>-0.3871</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0352</v>
+        <v>0.5511</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7665</v>
+        <v>-0.9382</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3169</v>
+        <v>0.5792</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>3.2823</v>
+        <v>1.5446</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7762</v>
+        <v>0.3379</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1588</v>
+        <v>0.379</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6173</v>
+        <v>-0.0411</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2277</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2856</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. SANCHEZ CASTILLO</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1877</v>
+        <v>1.4089</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1684</v>
+        <v>-0.0868</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0194</v>
+        <v>1.4957</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4711</v>
+        <v>0.3917</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6339</v>
+        <v>-0.1305</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1628</v>
+        <v>0.5221</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8582</v>
+        <v>2.0555</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0828</v>
+        <v>0.629</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7754</v>
+        <v>1.4265</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3871</v>
+        <v>-1.6638</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5511</v>
+        <v>-0.7594</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9382</v>
+        <v>-0.9044</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5446</v>
+        <v>3.2823</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0717</v>
+        <v>0.2139</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2756</v>
+        <v>0.1167</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2038</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.5482</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="X19" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3653</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.1778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2909</v>
+        <v>0.3791</v>
       </c>
       <c r="G20" t="n">
         <v>0.3156</v>
@@ -2014,13 +2014,13 @@
         <v>0.1931</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1434</v>
+        <v>0.0483</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0277</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1157</v>
+        <v>-0.0275</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. SOW</t>
+          <t>P. GRANJA I BERNAD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1061</v>
+        <v>-0.0232</v>
       </c>
       <c r="E21" t="n">
-        <v>0.537</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6431</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1597</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2622</v>
+        <v>1.2689</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8975</v>
+        <v>-0.6646</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5659999999999999</v>
+        <v>0.3083</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6067</v>
+        <v>0.3037</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0407</v>
+        <v>0.0046</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5937</v>
+        <v>0.2959</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3445</v>
+        <v>0.9651</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9382</v>
+        <v>-0.6692</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.3862</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0536</v>
+        <v>-0.0482</v>
       </c>
       <c r="T21" t="n">
-        <v>1.103</v>
+        <v>-0.0208</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0494</v>
+        <v>-0.0274</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. GRANJA I BERNAD</t>
+          <t>B. SOW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8079</v>
+        <v>-0.8701</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9882</v>
+        <v>-0.2903</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1802</v>
+        <v>-0.5797</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6042999999999999</v>
+        <v>-1.1597</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2689</v>
+        <v>-0.2622</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6646</v>
+        <v>-0.8975</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3083</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3037</v>
+        <v>-0.6067</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0046</v>
+        <v>0.0407</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2959</v>
+        <v>-0.5937</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9651</v>
+        <v>0.3445</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6692</v>
+        <v>-0.9382</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.833</v>
+        <v>0.2896</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3311</v>
+        <v>0.2757</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5019</v>
+        <v>0.014</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3376</v>
+        <v>-4.1101</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9282</v>
+        <v>-2.8247</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4095</v>
+        <v>-1.2853</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7979</v>
@@ -2248,13 +2248,13 @@
         <v>0.3862</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.4896</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3036</v>
+        <v>-0.2001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4136</v>
+        <v>-0.2895</v>
       </c>
       <c r="V23" t="n">
         <v>0.7221</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4103</v>
+        <v>-4.3276</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9031</v>
+        <v>-3.6963</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5071</v>
+        <v>-0.6313</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4002</v>
@@ -2326,13 +2326,13 @@
         <v>0.3862</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1103</v>
+        <v>-0.0276</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4966</v>
+        <v>-0.2898</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3863</v>
+        <v>0.2622</v>
       </c>
       <c r="V24" t="n">
         <v>0.6795</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>21.6662</v>
+        <v>23.7345</v>
       </c>
       <c r="E25" t="n">
-        <v>13.0327</v>
+        <v>13.0329</v>
       </c>
       <c r="F25" t="n">
-        <v>8.633400000000002</v>
+        <v>10.7017</v>
       </c>
       <c r="G25" t="n">
         <v>13.068</v>
       </c>
       <c r="H25" t="n">
-        <v>4.828099999999999</v>
+        <v>4.828100000000001</v>
       </c>
       <c r="I25" t="n">
         <v>8.239999999999998</v>
@@ -2380,7 +2380,7 @@
         <v>22.6661</v>
       </c>
       <c r="K25" t="n">
-        <v>7.2478</v>
+        <v>7.247799999999998</v>
       </c>
       <c r="L25" t="n">
         <v>15.4181</v>
@@ -2404,13 +2404,13 @@
         <v>20.2733</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3786</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5482</v>
+        <v>0.5484</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.926600000000001</v>
+        <v>0.1419</v>
       </c>
       <c r="V25" t="n">
         <v>7.0805</v>
